--- a/12 Week Upper Lower Program v4.xlsx
+++ b/12 Week Upper Lower Program v4.xlsx
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Seated Hamstring Curl</t>
+          <t>Glute Bridge March (single-leg)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Knee-flex. Dorsiflex foot.</t>
+          <t>Unilateral glute + core. Decompressed. No ham curl overlap.</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Nordic Hamstring Curl</t>
+          <t>Back Extension (45° hyper, BW or plate)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>slow 3s</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>BW eccentric. Heavy posterior. Standalone set — not in superset.</t>
+          <t>Glute + erector. Pause at top. No ham curl overlap.</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>KB Swing</t>
+          <t>Cable Glute Kickback</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>12–15</t>
+          <t>10–12</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>X010</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Hip ext + bracing. Glute lockout at top.</t>
+          <t>Pure glute isolation. No KB swing overlap with accessory.</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Light Ham Curl</t>
+          <t>Light Back Extension (BW)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>PEAK WEEK.</t>
+          <t>PEAK WEEK. Erector + glute. Accessory covers ham curl.</t>
         </is>
       </c>
     </row>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>Light Ham Curl</t>
+          <t>Light Glute Bridge</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -10939,7 +10939,7 @@
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>DELOAD.</t>
+          <t>DELOAD. Easy glute. Accessory covers ham curl.</t>
         </is>
       </c>
     </row>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Nordic Hamstring Curl</t>
+          <t>Reverse Hyper (loaded vs W1)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>slow 4s</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Longer eccentric vs W3. BW controlled.</t>
+          <t>Add load vs W1. Decompressed posterior chain.</t>
         </is>
       </c>
     </row>
@@ -15065,7 +15065,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Lying Ham Curl (drop set)</t>
+          <t>Glute Bridge (weighted, plate on hips)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Drop 20% final set.</t>
+          <t>Floor-based glute. Different from A1 hip thrust angle.</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Seated Ham Curl (paused)</t>
+          <t>Back Extension (paused at top, weighted)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Pause at peak flex.</t>
+          <t>Glute + erector. Pause peak contraction.</t>
         </is>
       </c>
     </row>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>RDL (DB, moderate — NOT BB)</t>
+          <t>Cable Glute Kickback (drop set)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -19212,7 +19212,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Light DB only. Spinal erectors partially recovered by B1 position.</t>
+          <t>Drop 20% final set. Glute isolation peak.</t>
         </is>
       </c>
     </row>
@@ -21068,7 +21068,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Light Ham Curl</t>
+          <t>Light Back Extension (BW)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -21078,7 +21078,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -21093,7 +21093,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>PEAK WEEK.</t>
+          <t>PEAK WEEK. Accessory covers ham curl.</t>
         </is>
       </c>
     </row>
@@ -23332,7 +23332,7 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>Light Ham Curl</t>
+          <t>Light Glute Bridge</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -23357,7 +23357,7 @@
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>DELOAD.</t>
+          <t>DELOAD. Accessory covers ham curl.</t>
         </is>
       </c>
     </row>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Lying Hamstring Curl</t>
+          <t>Reverse Hyper (or Hyper Bench)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -23739,7 +23739,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Knee-flex. Slow negative.</t>
+          <t>Posterior chain decompressed. Different stimulus from accessory ham curl.</t>
         </is>
       </c>
     </row>

--- a/12 Week Upper Lower Program v4.xlsx
+++ b/12 Week Upper Lower Program v4.xlsx
@@ -3396,7 +3396,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Knee-flex isolation. Save Nordics for standalone sets.</t>
+          <t>Knee-flex isolation.</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Hip-ext. Explosive glute snap.</t>
+          <t>Hip-ext. Explosive glute snap. No RDL pattern.</t>
         </is>
       </c>
     </row>
@@ -3482,28 +3482,28 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Sissy Squat (BW or light DB)</t>
+          <t>Seated Calf Raise</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3×10–12</t>
+          <t>3×15</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>75s</t>
+          <t>60s</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Advanced terminal ext.</t>
+          <t>Soleus emphasis. Knees bent.</t>
         </is>
       </c>
     </row>
@@ -3515,18 +3515,18 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Single-Leg Ham Curl</t>
+          <t>DB Goblet Squat</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr"/>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>3×10/leg</t>
+          <t>3×12</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>Optional. Unilateral.</t>
+          <t>Optional. Upright quad focus.</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Inverted Row (feet elevated)</t>
+          <t>DB Floor Press (neutral grip)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Horizontal pull BW. Note: B pairs pull+pull here for extra back volume on pull day.</t>
+          <t>Horizontal push. Tricep + chest. Corrects B2 from pull to push.</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Stiff-Leg DL (DB)</t>
+          <t>Glute-Ham Raise (BW)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Hip-ext ham. More knee than RDL.</t>
+          <t>Hip-ext + knee-flex combo. Posterior chain without spinal hinge.</t>
         </is>
       </c>
     </row>
@@ -5363,18 +5363,18 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Split Squat (BW)</t>
+          <t>Copenhagen Plank</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3×12/leg</t>
+          <t>3×20s/side</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>iso</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Bodyweight. Unilateral focus.</t>
+          <t>Adductor isometric. Build to 30s.</t>
         </is>
       </c>
     </row>
@@ -5396,18 +5396,18 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>KB Swing</t>
+          <t>Sissy Squat (BW)</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr"/>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>3×15</t>
+          <t>3×10</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>X010</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>Optional. Hip-ext power.</t>
+          <t>Optional. Terminal knee ext.</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Low-to-High Cable Fly</t>
+          <t>Pec Deck</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr"/>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>PEAK WK OPTIONAL. Upper pec.</t>
+          <t>PEAK WK OPTIONAL. Different stimulus from B1 cable fly.</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Single-Leg RDL (BW)</t>
+          <t>Light Swiss Ball Curl</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Balance + hip ext. Light.</t>
+          <t>PEAK WEEK. Easy floor-based ham.</t>
         </is>
       </c>
     </row>
@@ -7607,13 +7607,13 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Leg Extension (drop set)</t>
+          <t>Single-Leg Calf Raise (BW)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3×12 drop</t>
+          <t>2×12/side</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>90s</t>
+          <t>60s</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>PEAK WK. Drop 20% last set.</t>
+          <t>PEAK WK. Easy calf.</t>
         </is>
       </c>
     </row>
@@ -7640,13 +7640,13 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>RDL (light)</t>
+          <t>Light Leg Extension</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr"/>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>2×12</t>
+          <t>2×15</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>PEAK WK OPTIONAL.</t>
+          <t>PEAK WK OPTIONAL. Easy isolation.</t>
         </is>
       </c>
     </row>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Light RDL</t>
+          <t>Light Glute Bridge</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>DELOAD.</t>
+          <t>DELOAD. Easy hip-ext.</t>
         </is>
       </c>
     </row>
@@ -9488,13 +9488,13 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>Light Leg Extension</t>
+          <t>Light Calf Raise</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr"/>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>2×12</t>
+          <t>2×15</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="G9" s="20" t="inlineStr">
         <is>
-          <t>DELOAD.</t>
+          <t>DELOAD. Easy movement.</t>
         </is>
       </c>
     </row>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Light Ham Curl</t>
+          <t>Light BW Squat</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr"/>
@@ -9532,7 +9532,7 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Good Morning (BB, light)</t>
+          <t>Cable Pull-Through (heavier vs W2)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Hip-ext. Hinge under load.</t>
+          <t>Add load vs B1. Hip-ext. No RDL overlap.</t>
         </is>
       </c>
     </row>
@@ -11752,28 +11752,28 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>DB Lateral Lunge</t>
+          <t>Tibialis Raise (wall or band)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3×10/leg</t>
+          <t>3×15</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>75s</t>
+          <t>60s</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Adductor + quad. Step wide.</t>
+          <t>Shin / tib anterior. Knee health + shin splint prevention.</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Lying Ham Curl (add load vs W1)</t>
+          <t>Leg Extension (heavier)</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr"/>
@@ -11801,12 +11801,12 @@
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>60s</t>
+          <t>75s</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>Optional.</t>
+          <t>Optional. Add load vs B1.</t>
         </is>
       </c>
     </row>
@@ -13598,7 +13598,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Single-Leg RDL (BB)</t>
+          <t>Swiss Ball Hamstring Curl (feet elevated)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>10–12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Hip-ext. Add load B2.</t>
+          <t>Harder variation — elevated feet increase leverage.</t>
         </is>
       </c>
     </row>
@@ -13635,28 +13635,28 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Wall Sit (BW, 60s)</t>
+          <t>Adductor Machine (heavier)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3×60s</t>
+          <t>3×10</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>iso</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>60s</t>
+          <t>75s</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Isometric quad. Burn.</t>
+          <t>Add load vs W2. Adductor strength.</t>
         </is>
       </c>
     </row>
@@ -13668,18 +13668,18 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Stiff-Leg DL (DB)</t>
+          <t>DB Walking Lunge</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr"/>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>3×12</t>
+          <t>3×10/leg</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
@@ -13689,7 +13689,7 @@
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>Optional. Hip-ext ham.</t>
+          <t>Optional. Unilateral quad volume.</t>
         </is>
       </c>
     </row>
@@ -13982,7 +13982,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Single-Leg RDL (DB)</t>
+          <t>Swiss Ball Hamstring Curl</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Hip-ext ham. Balance focus.</t>
+          <t>Floor-based hip-ext + knee-flex. No RDL overlap.</t>
         </is>
       </c>
     </row>
@@ -14019,13 +14019,13 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Leg Extension</t>
+          <t>Standing Calf Raise</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3×12–15</t>
+          <t>3×15</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -14040,7 +14040,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>VMO isolation. Slow negative.</t>
+          <t>Gastrocnemius. Full ROM — stretch at bottom.</t>
         </is>
       </c>
     </row>
@@ -14052,13 +14052,13 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Lying Hamstring Curl (extra)</t>
+          <t>Leg Extension</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr"/>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>3×12</t>
+          <t>3×12–15</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>Optional. Knee-flex.</t>
+          <t>Optional. Quad isolation.</t>
         </is>
       </c>
     </row>
@@ -15554,18 +15554,18 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Weighted Dip (chest lean)</t>
+          <t>Incline DB Fly</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr"/>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>3×8–10</t>
+          <t>3×10–12</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
@@ -15575,7 +15575,7 @@
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>Optional. Chest bias dip.</t>
+          <t>Optional. Different from A1 dip pattern.</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>KB Single-Leg RDL</t>
+          <t>Band-Assisted GHR</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Hip-ext balance work.</t>
+          <t>GHR with band decel. Hip-ext + knee-flex combo.</t>
         </is>
       </c>
     </row>
@@ -15903,28 +15903,28 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BW Pistol Squat (parallette assist)</t>
+          <t>Single-Leg Calf Raise (weighted)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3×6/leg</t>
+          <t>3×12/side</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>controlled</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>75s</t>
+          <t>60s</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Skill + strength.</t>
+          <t>Add load. Full stretch.</t>
         </is>
       </c>
     </row>
@@ -15936,28 +15936,28 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Seated Ham Curl</t>
+          <t>BW Pistol Squat (parallette assist)</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr"/>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>3×10–12</t>
+          <t>3×5/leg</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>controlled</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>60s</t>
+          <t>75s</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>Optional.</t>
+          <t>Optional. Skill + strength.</t>
         </is>
       </c>
     </row>
@@ -17749,7 +17749,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Stiff-Leg DL (BB)</t>
+          <t>KB Swing (heavy)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -17759,12 +17759,12 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>8–10</t>
+          <t>10–12</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>X010</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -17774,7 +17774,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Add load vs W4.</t>
+          <t>Heaviest swing of program. Hip-ext dominant.</t>
         </is>
       </c>
     </row>
@@ -17786,18 +17786,18 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Leg Extension (paused)</t>
+          <t>Copenhagen Plank (weighted)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3×10+2s</t>
+          <t>3×25s/side</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>iso</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -17807,7 +17807,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Pause at top. VMO squeeze.</t>
+          <t>Add light plate. Adductor peak.</t>
         </is>
       </c>
     </row>
@@ -17819,28 +17819,28 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>SL RDL (KB)</t>
+          <t>Leg Press (slow eccentric)</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr"/>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>3×10/leg</t>
+          <t>3×10</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>60s</t>
+          <t>75s</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>Optional. Balance focus.</t>
+          <t>Optional. Eccentric quad overload.</t>
         </is>
       </c>
     </row>
@@ -19988,7 +19988,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Single-Leg RDL (BW)</t>
+          <t>Light Cable Pull-Through</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -20003,7 +20003,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -20013,7 +20013,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>PEAK WEEK. Light.</t>
+          <t>PEAK WEEK. Easy hip-ext.</t>
         </is>
       </c>
     </row>
@@ -20025,18 +20025,18 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Light BW Squat</t>
+          <t>Light Calf Raise</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2×15</t>
+          <t>2×12</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -20046,7 +20046,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>PEAK WK. Active recovery.</t>
+          <t>PEAK WK. Easy.</t>
         </is>
       </c>
     </row>
@@ -20058,13 +20058,13 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Light Ham Curl</t>
+          <t>Light Leg Extension</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr"/>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>2×10</t>
+          <t>2×12</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Light RDL</t>
+          <t>Light Glute Bridge</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -21894,7 +21894,7 @@
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>DELOAD.</t>
+          <t>DELOAD. End of program.</t>
         </is>
       </c>
     </row>
@@ -21906,7 +21906,7 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>Light Leg Extension</t>
+          <t>Light Calf Raise</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr"/>
@@ -21939,18 +21939,18 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Light RDL</t>
+          <t>Light BW Squat</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr"/>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>2×12</t>
+          <t>2×10</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -23857,7 +23857,7 @@
           <t>AB ROUTINE — 3 rounds, 60s rest between rounds:
   • Hanging Knee Raise — 3×12 [Hip flexion. Full dead hang. No swinging.]
   • Pallof Press — 3×10/side [Anti-rotation. Cable or band.]
-  • KB KB Swing (core focus) — 3×12 [KB — hip ext + anterior bracing. Squeeze glutes at top.]</t>
+  • KB Swing (core focus) — 3×12 [KB — hip ext + anterior bracing. Squeeze glutes at top.]</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -24515,7 +24515,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>RDL (BB)</t>
+          <t>Cable Pull-Through (rope)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -24525,7 +24525,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>10–12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -24540,7 +24540,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Hip-ext ham. Hinge, not squat.</t>
+          <t>Hip-ext. Spine neutral. Different stimulus from light-lift RDL.</t>
         </is>
       </c>
     </row>
@@ -24552,28 +24552,28 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Goblet Squat (paused)</t>
+          <t>Adductor Machine</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3×10</t>
+          <t>3×12</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2010+2s</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>75s</t>
+          <t>60s</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Pause at bottom. Quad stretch.</t>
+          <t>Inner thigh. Important for squat stability.</t>
         </is>
       </c>
     </row>
@@ -24585,28 +24585,28 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Nordic Ham Curl</t>
+          <t>BW Split Squat</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr"/>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>3×6–8</t>
+          <t>3×10/leg</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>75s</t>
+          <t>60s</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>Optional. Eccentric emphasis.</t>
+          <t>Optional. Unilateral quad.</t>
         </is>
       </c>
     </row>

--- a/12 Week Upper Lower Program v4.xlsx
+++ b/12 Week Upper Lower Program v4.xlsx
@@ -176,7 +176,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -198,11 +198,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -258,6 +302,8 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -717,12 +763,12 @@
           <t>─── BENCH PRESS PROGRESSION (Monday Heavy) ───</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="21" t="n"/>
+      <c r="E7" s="21" t="n"/>
+      <c r="F7" s="21" t="n"/>
+      <c r="G7" s="22" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -969,12 +1015,12 @@
           <t>─── BACK SQUAT PROGRESSION (Tuesday Heavy) ───</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
+      <c r="B23" s="21" t="n"/>
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="21" t="n"/>
+      <c r="F23" s="21" t="n"/>
+      <c r="G23" s="22" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1221,12 +1267,12 @@
           <t>─── KEY CHANGES FROM PREVIOUS VERSION ───</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="2" t="n"/>
+      <c r="B39" s="21" t="n"/>
+      <c r="C39" s="21" t="n"/>
+      <c r="D39" s="21" t="n"/>
+      <c r="E39" s="21" t="n"/>
+      <c r="F39" s="21" t="n"/>
+      <c r="G39" s="22" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1328,12 +1374,12 @@
           <t>─── IWT REDESIGN (Wednesday) ───</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n"/>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="n"/>
-      <c r="G46" s="2" t="n"/>
+      <c r="B46" s="21" t="n"/>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="22" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1546,12 +1592,12 @@
           <t>─── DAILY STRUCTURE ───</t>
         </is>
       </c>
-      <c r="B60" s="2" t="n"/>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
-      <c r="F60" s="2" t="n"/>
-      <c r="G60" s="2" t="n"/>
+      <c r="B60" s="21" t="n"/>
+      <c r="C60" s="21" t="n"/>
+      <c r="D60" s="21" t="n"/>
+      <c r="E60" s="21" t="n"/>
+      <c r="F60" s="21" t="n"/>
+      <c r="G60" s="22" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -1653,12 +1699,12 @@
           <t>─── ON WEEK EXTENSION ───</t>
         </is>
       </c>
-      <c r="B67" s="2" t="n"/>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="n"/>
-      <c r="F67" s="2" t="n"/>
-      <c r="G67" s="2" t="n"/>
+      <c r="B67" s="21" t="n"/>
+      <c r="C67" s="21" t="n"/>
+      <c r="D67" s="21" t="n"/>
+      <c r="E67" s="21" t="n"/>
+      <c r="F67" s="21" t="n"/>
+      <c r="G67" s="22" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -3026,7 +3072,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Weighted Dip (slight forward lean)</t>
+          <t>Cable Fly (mid)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -3036,22 +3082,22 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>8–10</t>
+          <t>10–12</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2011+1s</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>45s</t>
+          <t>60s</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Chest bias. Control descent. Tricep + pec.</t>
+          <t>Chest isolation. Mid-chest fibers. Pause 1s peak contraction.</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3109,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Close-Grip Lat Pulldown</t>
+          <t>Kelso Shrug (chest-supported DB)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -3073,7 +3119,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>10–12</t>
+          <t>12–15</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -3088,7 +3134,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Elbows track beside torso.</t>
+          <t>Scapular retraction isolation. Mid/lower trap. Chest on bench, retract blades only.</t>
         </is>
       </c>
     </row>
@@ -4907,7 +4953,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Banded Push-Up (max reps capped 20)</t>
+          <t>DB Fly (flat)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -4917,22 +4963,22 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>12–15</t>
+          <t>10–12</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>X010</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>45s</t>
+          <t>60s</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>BW + band resistance.</t>
+          <t>Chest isolation. Free-weight stretch at bottom. Different from A1 cable.</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4990,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Chest-Supported DB Row</t>
+          <t>Cable Y-Raise</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -4954,7 +5000,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>8–10</t>
+          <t>12–15</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -4969,7 +5015,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>No momentum. Chest on pad.</t>
+          <t>Lower trap. Scapular depression at 45° angle. Slow and controlled.</t>
         </is>
       </c>
     </row>
@@ -5396,10 +5442,14 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Sissy Squat (BW)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr"/>
+          <t>BW Step-Up (high box, slow 3s ascent)</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>3×10/leg</t>
+        </is>
+      </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
           <t>3×10</t>
@@ -5407,7 +5457,7 @@
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
@@ -5417,7 +5467,7 @@
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>Optional. Terminal knee ext.</t>
+          <t>Optional. Unilateral quad with slow tempo. Different from A1 hack squat and B1 reverse lunge.</t>
         </is>
       </c>
     </row>
@@ -7151,17 +7201,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Low-to-High Cable Fly</t>
+          <t>Light Cable Crossover</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10–12</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -7171,12 +7221,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>45s</t>
+          <t>60s</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Upper pec. Squeeze at top. Low CNS cost.</t>
+          <t>PEAK WK. Easy chest isolation.</t>
         </is>
       </c>
     </row>
@@ -7188,17 +7238,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Rear Delt Cable Fly</t>
+          <t>Light DB Trap-3 Raise (prone)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10–12</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -7213,7 +7263,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Light, feel the contraction.</t>
+          <t>PEAK WK. Lower trap. Lie on incline bench, raise DBs in Y pattern.</t>
         </is>
       </c>
     </row>
@@ -7258,10 +7308,14 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Pec Deck</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr"/>
+          <t>Light DB Squeeze Press</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>3×12</t>
+        </is>
+      </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
           <t>3×12</t>
@@ -7269,7 +7323,7 @@
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
@@ -7279,7 +7333,7 @@
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>PEAK WK OPTIONAL. Different stimulus from B1 cable fly.</t>
+          <t>PEAK WK OPTIONAL. Squeeze 2 DBs together. Different from A1 pec deck.</t>
         </is>
       </c>
     </row>
@@ -7640,10 +7694,14 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Light Leg Extension</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr"/>
+          <t>Light Goblet Squat</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>2×12</t>
+        </is>
+      </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
           <t>2×15</t>
@@ -7651,7 +7709,7 @@
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
@@ -7661,7 +7719,7 @@
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>PEAK WK OPTIONAL. Easy isolation.</t>
+          <t>PEAK WK OPTIONAL. Easy bilateral quad. Different from A1 leg extension.</t>
         </is>
       </c>
     </row>
@@ -9032,7 +9090,7 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>Light Lateral Raise</t>
+          <t>Light DB Fly (flat)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -9042,7 +9100,7 @@
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10–12</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -9052,12 +9110,12 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>45s</t>
+          <t>60s</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>DELOAD.</t>
+          <t>DELOAD. Easy chest isolation.</t>
         </is>
       </c>
     </row>
@@ -9069,7 +9127,7 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Light Face Pull</t>
+          <t>Light Cable Y-Raise</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -9079,7 +9137,7 @@
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10–12</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -9089,12 +9147,12 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>60s</t>
+          <t>90s</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>DELOAD.</t>
+          <t>DELOAD. Lower trap. Light cable only.</t>
         </is>
       </c>
     </row>
@@ -9797,7 +9855,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Parallette Push-Up (feet elevated)</t>
+          <t>Pec Deck</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -9807,22 +9865,22 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10–12</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>X010</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>45s</t>
+          <t>60s</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>BW. Max control.</t>
+          <t>Chest isolation. Machine = pure pec, no triceps. Squeeze 1s at peak.</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9892,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>One-Arm DB Row</t>
+          <t>Snatch-Grip BB Shrug</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -9844,7 +9902,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>10–12</t>
+          <t>12–15</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -9859,7 +9917,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Full ROM, let shoulder drop.</t>
+          <t>Upper trap focus. Wide grip elevates traps and rear delt. Pause 1s at top.</t>
         </is>
       </c>
     </row>
@@ -10639,10 +10697,14 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Light Row</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr"/>
+          <t>Light Reverse Pec Deck</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>2×12</t>
+        </is>
+      </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
           <t>2×12</t>
@@ -10660,7 +10722,7 @@
       </c>
       <c r="G10" s="20" t="inlineStr">
         <is>
-          <t>DELOAD OPTIONAL.</t>
+          <t>DELOAD OPTIONAL. Rear delt + mid trap. Different from A1 light row.</t>
         </is>
       </c>
     </row>
@@ -11296,7 +11358,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Parallette Dip (ring or bar)</t>
+          <t>Incline DB Fly</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -11311,17 +11373,17 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>45s</t>
+          <t>60s</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>BW or weighted. Chest bias, slight lean.</t>
+          <t>Chest isolation. Upper pec stretch. Free weight vs A1 press, no triceps.</t>
         </is>
       </c>
     </row>
@@ -11333,7 +11395,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>One-Arm DB Row (elbow out)</t>
+          <t>Snatch-Grip DB Shrug</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -11343,7 +11405,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>10–12</t>
+          <t>12–15</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -11358,7 +11420,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Elbow flares — upper back emphasis.</t>
+          <t>Upper trap. DB version for unilateral control. Pause at top.</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13204,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Seated Cable Row (neutral)</t>
+          <t>Chest-Supported T-Bar Row</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -13152,7 +13214,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -13167,7 +13229,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Mid-back emphasis.</t>
+          <t>Pull. Different equipment &amp; angle from light-lift seated row.</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13241,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Pseudo-Planche Lean (parallettes)</t>
+          <t>High-to-Low Cable Fly (decline angle)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -13189,12 +13251,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10–12</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>hold 3s</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -13204,7 +13266,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>BW. Protract, lean forward 20°.</t>
+          <t>Chest isolation. Lower pec fibers. Different from A1 incline press.</t>
         </is>
       </c>
     </row>
@@ -13216,7 +13278,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Chest-Supported Row (pronated)</t>
+          <t>Cable Pull-to-Face (high cable)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -13226,12 +13288,12 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>10–12</t>
+          <t>12–15</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2011+1s</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -13241,7 +13303,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Overhand — more rhomboids.</t>
+          <t>Upper back + posterior delt. High cable to face. Different from cable row.</t>
         </is>
       </c>
     </row>
@@ -15447,7 +15509,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Incline DB Press (steep 45°)</t>
+          <t>Low-to-High Cable Fly</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -15457,22 +15519,22 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>8–10</t>
+          <t>10–12</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>45s</t>
+          <t>60s</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Upper pec. Full ROM.</t>
+          <t>Chest isolation. Upper pec emphasis. Different from A1 dip pattern.</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15546,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Straight-Arm Pulldown</t>
+          <t>Powell Raise (kneeling neutral DB)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -15494,7 +15556,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>10–12</t>
+          <t>10–12/side</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -15509,7 +15571,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Keep arms straight. Lats.</t>
+          <t>Rhomboid + mid trap. Half-kneeling, lateral raise with neutral grip.</t>
         </is>
       </c>
     </row>
@@ -16290,10 +16352,14 @@
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>Lateral Raise (cable seated)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr"/>
+          <t>DB Front Raise</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>3×12</t>
+        </is>
+      </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
           <t>3×12</t>
@@ -16311,7 +16377,7 @@
       </c>
       <c r="G9" s="16" t="inlineStr">
         <is>
-          <t>Optional.</t>
+          <t>Optional. Anterior delt isolation. Different from A1 lateral raise.</t>
         </is>
       </c>
     </row>
@@ -17330,7 +17396,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Archer Push-Up (parallettes)</t>
+          <t>Pec Deck (paused at peak)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -17340,12 +17406,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>10–12</t>
+          <t>8–10+2s</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>X010</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -17355,7 +17421,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>BW advanced. One arm assists.</t>
+          <t>Chest isolation with 2s peak hold. Different from A1 cable fly.</t>
         </is>
       </c>
     </row>
@@ -17367,7 +17433,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Chest-Supported T-Bar Row</t>
+          <t>Bent-Over DB Reverse Fly</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -17377,7 +17443,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>8–10</t>
+          <t>12–15</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -17392,7 +17458,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Loaded. Control the negative.</t>
+          <t>Rear delt + mid trap. Chest down, retract and lift. Distinct from lat work.</t>
         </is>
       </c>
     </row>
@@ -17819,10 +17885,14 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Leg Press (slow eccentric)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr"/>
+          <t>Sissy Squat (DB held)</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>3×10</t>
+        </is>
+      </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
           <t>3×10</t>
@@ -17830,7 +17900,7 @@
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
@@ -17840,7 +17910,7 @@
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>Optional. Eccentric quad overload.</t>
+          <t>Optional. Terminal knee extension with light DB. Different from A1 leg press.</t>
         </is>
       </c>
     </row>
@@ -19569,7 +19639,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Light Cable Fly (low-to-high)</t>
+          <t>Light Incline DB Fly</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -19579,7 +19649,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10–12</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -19589,12 +19659,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>45s</t>
+          <t>60s</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>PEAK WEEK. Upper pec. Feather-light.</t>
+          <t>PEAK WK. Easy chest isolation.</t>
         </is>
       </c>
     </row>
@@ -19606,7 +19676,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Rear Delt DB Fly</t>
+          <t>Light Cable Reverse Fly</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -19616,7 +19686,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10–12</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -19626,12 +19696,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>60s</t>
+          <t>90s</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Control only.</t>
+          <t>PEAK WK. Rear delt + mid trap. Light cable.</t>
         </is>
       </c>
     </row>
@@ -19676,10 +19746,14 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Light Cable Fly</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr"/>
+          <t>Light DB Squeeze Press</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>2×12</t>
+        </is>
+      </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
           <t>2×12</t>
@@ -19687,7 +19761,7 @@
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
@@ -19697,7 +19771,7 @@
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>PEAK WK OPTIONAL.</t>
+          <t>PEAK WK OPTIONAL. Inner-pec squeeze. Different from B1 incline fly and A1 pec deck.</t>
         </is>
       </c>
     </row>
@@ -20058,10 +20132,14 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Light Leg Extension</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr"/>
+          <t>Light BW Squat (slow 3s descent)</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>2×10</t>
+        </is>
+      </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
           <t>2×12</t>
@@ -20069,7 +20147,7 @@
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
@@ -20079,7 +20157,7 @@
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>PEAK WK OPTIONAL.</t>
+          <t>PEAK WK OPTIONAL. Bilateral BW. Different from A1 leg extension and B1 pistol assist.</t>
         </is>
       </c>
     </row>
@@ -21175,10 +21253,14 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Light Leg Press</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr"/>
+          <t>Light BW Squat</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>2×10</t>
+        </is>
+      </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
           <t>2×12</t>
@@ -21196,7 +21278,7 @@
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>PEAK WK OPTIONAL.</t>
+          <t>PEAK WK OPTIONAL. BW only. Different from B2 leg press.</t>
         </is>
       </c>
     </row>
@@ -21450,7 +21532,7 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>Light Lateral Raise</t>
+          <t>Light Pec Deck</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -21460,7 +21542,7 @@
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10–12</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -21470,12 +21552,12 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>45s</t>
+          <t>60s</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>DELOAD.</t>
+          <t>DELOAD. Easy chest isolation.</t>
         </is>
       </c>
     </row>
@@ -21487,7 +21569,7 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Light Face Pull</t>
+          <t>Light Cable Y-Raise</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -21497,7 +21579,7 @@
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10–12</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -21507,12 +21589,12 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>60s</t>
+          <t>90s</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>DELOAD.</t>
+          <t>DELOAD. Lower trap. End of program.</t>
         </is>
       </c>
     </row>
@@ -23057,13 +23139,17 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Light Row</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr"/>
+          <t>Light Face Pull</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>2×15</t>
+        </is>
+      </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>2×12</t>
+          <t>2×15</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -23078,7 +23164,7 @@
       </c>
       <c r="G10" s="20" t="inlineStr">
         <is>
-          <t>DELOAD OPTIONAL.</t>
+          <t>DELOAD OPTIONAL. External rotation + rear delt. Different from B1 band pull-apart.</t>
         </is>
       </c>
     </row>
@@ -24096,7 +24182,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Flat DB Press</t>
+          <t>Cable Crossover (high-to-low)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -24111,17 +24197,17 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>45s</t>
+          <t>60s</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Full stretch at bottom.</t>
+          <t>Chest isolation. Constant tension. Lower-mid pec emphasis.</t>
         </is>
       </c>
     </row>
@@ -24133,7 +24219,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Straight-Arm Pulldown</t>
+          <t>Cable Reverse Fly</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -24143,7 +24229,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>12–15</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -24158,7 +24244,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Lats only, arms straight.</t>
+          <t>Mid trap + rear delt. Squeeze blades at peak. Distinct from lat pulldown in A2.</t>
         </is>
       </c>
     </row>
